--- a/diseases/d200/2020-2025.xlsx
+++ b/diseases/d200/2020-2025.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24460,7 +24460,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -25266,7 +25266,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26311,7 +26311,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27192,7 +27192,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27834,7 +27834,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28237,7 +28237,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28476,7 +28476,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29521,7 +29521,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29760,7 +29760,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30163,7 +30163,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31447,7 +31447,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31686,7 +31686,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32089,7 +32089,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32328,7 +32328,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33373,7 +33373,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -34015,7 +34015,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34418,7 +34418,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -35299,7 +35299,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -35941,7 +35941,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36344,7 +36344,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -36583,7 +36583,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -37225,7 +37225,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -37867,7 +37867,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38270,7 +38270,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -39076,7 +39076,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -39479,7 +39479,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
